--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.51850654559615</v>
+        <v>9.834257313659375</v>
       </c>
       <c r="D2" t="n">
-        <v>28.99208284849754</v>
+        <v>4.71121346288085</v>
       </c>
       <c r="E2" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F2" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.72432974272625</v>
+        <v>10.19270358319302</v>
       </c>
       <c r="D3" t="n">
-        <v>40.65252474093793</v>
+        <v>6.606035270402414</v>
       </c>
       <c r="E3" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F3" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.64287743779231</v>
+        <v>8.066967583641251</v>
       </c>
       <c r="D4" t="n">
-        <v>8.65972200933164</v>
+        <v>1.407204826516391</v>
       </c>
       <c r="E4" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F4" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.39250195369485</v>
+        <v>7.701281567475413</v>
       </c>
       <c r="D5" t="n">
-        <v>12.10938385294391</v>
+        <v>1.967774876103385</v>
       </c>
       <c r="E5" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F5" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>72.94848480225272</v>
+        <v>11.85412878036607</v>
       </c>
       <c r="D6" t="n">
-        <v>60.73900533668405</v>
+        <v>9.870088367211158</v>
       </c>
       <c r="E6" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F6" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>64.72489006641794</v>
+        <v>10.51779463579292</v>
       </c>
       <c r="D7" t="n">
-        <v>50.01341558127331</v>
+        <v>8.127180031956913</v>
       </c>
       <c r="E7" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F7" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.19098594693583</v>
+        <v>7.506035216377072</v>
       </c>
       <c r="D8" t="n">
-        <v>29.68167050632582</v>
+        <v>4.823271457277945</v>
       </c>
       <c r="E8" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F8" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.17082746967134</v>
+        <v>7.827759463821594</v>
       </c>
       <c r="D9" t="n">
-        <v>34.88119497475128</v>
+        <v>5.668194183397083</v>
       </c>
       <c r="E9" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F9" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>69.90604760395735</v>
+        <v>11.35973273564307</v>
       </c>
       <c r="D10" t="n">
-        <v>66.97620978197558</v>
+        <v>10.88363408957103</v>
       </c>
       <c r="E10" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F10" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.50655092693508</v>
+        <v>9.01981452562695</v>
       </c>
       <c r="D11" t="n">
-        <v>55.1314954452969</v>
+        <v>8.958868009860746</v>
       </c>
       <c r="E11" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F11" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.93647704831755</v>
+        <v>5.189677520351601</v>
       </c>
       <c r="D12" t="n">
-        <v>28.55593953722413</v>
+        <v>4.640340174798922</v>
       </c>
       <c r="E12" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F12" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.68159322787388</v>
+        <v>7.748258899529506</v>
       </c>
       <c r="D13" t="n">
-        <v>47.21579771839757</v>
+        <v>7.672567129239606</v>
       </c>
       <c r="E13" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F13" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.68392425004699</v>
+        <v>5.798637690632635</v>
       </c>
       <c r="D14" t="n">
-        <v>35.176793131527</v>
+        <v>5.716228883873137</v>
       </c>
       <c r="E14" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F14" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>27.32445400952531</v>
+        <v>4.440223776547863</v>
       </c>
       <c r="D15" t="n">
-        <v>27.50047793728856</v>
+        <v>4.468827664809391</v>
       </c>
       <c r="E15" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F15" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>40.85427735224631</v>
+        <v>6.638820069740026</v>
       </c>
       <c r="D16" t="n">
-        <v>39.7209422454716</v>
+        <v>6.454653114889135</v>
       </c>
       <c r="E16" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F16" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>59.34169454269984</v>
+        <v>9.643025363188725</v>
       </c>
       <c r="D17" t="n">
-        <v>58.93670549951968</v>
+        <v>9.577214643671947</v>
       </c>
       <c r="E17" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F17" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>10.37125783694433</v>
+        <v>1.685329398503454</v>
       </c>
       <c r="D18" t="n">
-        <v>10.12904296847141</v>
+        <v>1.645969482376605</v>
       </c>
       <c r="E18" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F18" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>50.57578179249422</v>
+        <v>8.21856454128031</v>
       </c>
       <c r="D19" t="n">
-        <v>49.13043944837325</v>
+        <v>7.983696410360654</v>
       </c>
       <c r="E19" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F19" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>42.08163621028197</v>
+        <v>6.838265884170821</v>
       </c>
       <c r="D20" t="n">
-        <v>41.65919177755194</v>
+        <v>6.76961866385219</v>
       </c>
       <c r="E20" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F20" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>6.896984963488494</v>
+        <v>1.12076005656688</v>
       </c>
       <c r="D21" t="n">
-        <v>6.472989209964897</v>
+        <v>1.051860746619296</v>
       </c>
       <c r="E21" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F21" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>19.76645818663981</v>
+        <v>3.212049455328969</v>
       </c>
       <c r="D22" t="n">
-        <v>19.30652385271746</v>
+        <v>3.137310126066588</v>
       </c>
       <c r="E22" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F22" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>30.73389979224005</v>
+        <v>4.994258716239009</v>
       </c>
       <c r="D23" t="n">
-        <v>30.35469132178327</v>
+        <v>4.932637339789783</v>
       </c>
       <c r="E23" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F23" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>45.95636402842189</v>
+        <v>7.467909154618557</v>
       </c>
       <c r="D24" t="n">
-        <v>45.5968446989418</v>
+        <v>7.409487263578043</v>
       </c>
       <c r="E24" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F24" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>11.13047521644752</v>
+        <v>1.808702222672722</v>
       </c>
       <c r="D25" t="n">
-        <v>10.90323131658786</v>
+        <v>1.771775088945528</v>
       </c>
       <c r="E25" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F25" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>23.48415846290338</v>
+        <v>3.8161757502218</v>
       </c>
       <c r="D26" t="n">
-        <v>23.94602443240212</v>
+        <v>3.891228970265345</v>
       </c>
       <c r="E26" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F26" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>17.13487349394136</v>
+        <v>2.784416942765472</v>
       </c>
       <c r="D27" t="n">
-        <v>17.6582728115658</v>
+        <v>2.869469331879442</v>
       </c>
       <c r="E27" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F27" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>10.97735187744098</v>
+        <v>1.78381968008416</v>
       </c>
       <c r="D28" t="n">
-        <v>9.87903790312388</v>
+        <v>1.60534365925763</v>
       </c>
       <c r="E28" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F28" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>36.07095857109589</v>
+        <v>5.861530767803082</v>
       </c>
       <c r="D29" t="n">
-        <v>36.57146082884575</v>
+        <v>5.942862384687435</v>
       </c>
       <c r="E29" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F29" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>34.48817697696701</v>
+        <v>5.60432875875714</v>
       </c>
       <c r="D30" t="n">
-        <v>34.03953932719893</v>
+        <v>5.531425140669826</v>
       </c>
       <c r="E30" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F30" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>2.406397450018382</v>
+        <v>0.3910395856279871</v>
       </c>
       <c r="D31" t="n">
-        <v>3.336439523460899</v>
+        <v>0.5421714225623961</v>
       </c>
       <c r="E31" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F31" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>9.966539575193696</v>
+        <v>1.619562680968976</v>
       </c>
       <c r="D32" t="n">
-        <v>11.30123893014949</v>
+        <v>1.836451326149292</v>
       </c>
       <c r="E32" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F32" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>37.56577191097301</v>
+        <v>6.104437935533114</v>
       </c>
       <c r="D33" t="n">
-        <v>38.07332306186817</v>
+        <v>6.186914997553577</v>
       </c>
       <c r="E33" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F33" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>30.74460797681648</v>
+        <v>4.995998796232677</v>
       </c>
       <c r="D34" t="n">
-        <v>31.1899079981141</v>
+        <v>5.068360049693541</v>
       </c>
       <c r="E34" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F34" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>15.66306960435034</v>
+        <v>2.545248810706931</v>
       </c>
       <c r="D35" t="n">
-        <v>17.18265571125733</v>
+        <v>2.792181553079316</v>
       </c>
       <c r="E35" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F35" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>52.32127609105348</v>
+        <v>8.50220736479619</v>
       </c>
       <c r="D36" t="n">
-        <v>52.20892671723193</v>
+        <v>8.483950591550188</v>
       </c>
       <c r="E36" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F36" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>75.06958688526224</v>
+        <v>12.19880786885511</v>
       </c>
       <c r="D37" t="n">
-        <v>75.00308249478131</v>
+        <v>12.18800090540196</v>
       </c>
       <c r="E37" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F37" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>47.67351999950409</v>
+        <v>7.746946999919415</v>
       </c>
       <c r="D38" t="n">
-        <v>48.70676107692577</v>
+        <v>7.914848675000439</v>
       </c>
       <c r="E38" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F38" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>31.61644116546468</v>
+        <v>5.137671689388011</v>
       </c>
       <c r="D39" t="n">
-        <v>32.67092932171357</v>
+        <v>5.309026014778454</v>
       </c>
       <c r="E39" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F39" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>53.56538577406056</v>
+        <v>8.704375188284841</v>
       </c>
       <c r="D40" t="n">
-        <v>54.02480547480052</v>
+        <v>8.779030889655084</v>
       </c>
       <c r="E40" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F40" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>26.89711590326003</v>
+        <v>4.370781334279754</v>
       </c>
       <c r="D41" t="n">
-        <v>27.14521545597477</v>
+        <v>4.411097511595901</v>
       </c>
       <c r="E41" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F41" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>56.91404898347632</v>
+        <v>9.248532959814902</v>
       </c>
       <c r="D42" t="n">
-        <v>57.09008883054897</v>
+        <v>9.277139434964209</v>
       </c>
       <c r="E42" t="n">
-        <v>19.09652908610751</v>
+        <v>3.10318597649247</v>
       </c>
       <c r="F42" t="n">
-        <v>17.84518190970946</v>
+        <v>2.899842060327787</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
